--- a/docs/planillas/CLNecesidades_Candidatas_PT.xlsx
+++ b/docs/planillas/CLNecesidades_Candidatas_PT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emiliano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gestion-gym-app\docs\planillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8FFE56-0BED-4AB2-A620-A778F37BD80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DEEF86-C69D-4E99-AC60-002C46C5BCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25920" yWindow="240" windowWidth="25440" windowHeight="20520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54330" yWindow="-7260" windowWidth="25440" windowHeight="20520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perfiles Clientes" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="217">
   <si>
     <t>ID</t>
   </si>
@@ -672,6 +672,9 @@
   </si>
   <si>
     <t>N3, N5, P6, P7</t>
+  </si>
+  <si>
+    <t>P1, P9</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1550,7 @@
         <v>205</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>198</v>
